--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R472"/>
+  <dimension ref="A1:R477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28615,7 +28615,7 @@
         <v>283.3</v>
       </c>
       <c r="C472" t="n">
-        <v>335.43</v>
+        <v>322.72</v>
       </c>
       <c r="D472" t="n">
         <v>340.64</v>
@@ -28639,16 +28639,16 @@
         <v>330.01</v>
       </c>
       <c r="K472" t="n">
-        <v>319.35</v>
+        <v>310.56</v>
       </c>
       <c r="L472" t="n">
         <v>301.79</v>
       </c>
       <c r="M472" t="n">
-        <v>319.19</v>
+        <v>310.97</v>
       </c>
       <c r="N472" t="n">
-        <v>322.83</v>
+        <v>313.74</v>
       </c>
       <c r="O472" t="n">
         <v>308.25</v>
@@ -28660,6 +28660,306 @@
         <v>310.3</v>
       </c>
       <c r="R472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="C473" t="n">
+        <v>313.63</v>
+      </c>
+      <c r="D473" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="E473" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="F473" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="G473" t="n">
+        <v>338.72</v>
+      </c>
+      <c r="H473" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="I473" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="J473" t="n">
+        <v>322.65</v>
+      </c>
+      <c r="K473" t="n">
+        <v>304.59</v>
+      </c>
+      <c r="L473" t="n">
+        <v>296.6</v>
+      </c>
+      <c r="M473" t="n">
+        <v>305.93</v>
+      </c>
+      <c r="N473" t="n">
+        <v>308.04</v>
+      </c>
+      <c r="O473" t="n">
+        <v>305.79</v>
+      </c>
+      <c r="P473" t="n">
+        <v>305.56</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>274.52</v>
+      </c>
+      <c r="C474" t="n">
+        <v>300.79</v>
+      </c>
+      <c r="D474" t="n">
+        <v>338.13</v>
+      </c>
+      <c r="E474" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="F474" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="G474" t="n">
+        <v>337.16</v>
+      </c>
+      <c r="H474" t="n">
+        <v>335.99</v>
+      </c>
+      <c r="I474" t="n">
+        <v>330.16</v>
+      </c>
+      <c r="J474" t="n">
+        <v>315.57</v>
+      </c>
+      <c r="K474" t="n">
+        <v>298.27</v>
+      </c>
+      <c r="L474" t="n">
+        <v>288.7</v>
+      </c>
+      <c r="M474" t="n">
+        <v>298.82</v>
+      </c>
+      <c r="N474" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="O474" t="n">
+        <v>301.36</v>
+      </c>
+      <c r="P474" t="n">
+        <v>300.95</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>270.26</v>
+      </c>
+      <c r="C475" t="n">
+        <v>293.44</v>
+      </c>
+      <c r="D475" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="E475" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="F475" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="G475" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="H475" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="I475" t="n">
+        <v>330.16</v>
+      </c>
+      <c r="J475" t="n">
+        <v>309.66</v>
+      </c>
+      <c r="K475" t="n">
+        <v>293.23</v>
+      </c>
+      <c r="L475" t="n">
+        <v>284.14</v>
+      </c>
+      <c r="M475" t="n">
+        <v>294.79</v>
+      </c>
+      <c r="N475" t="n">
+        <v>294.89</v>
+      </c>
+      <c r="O475" t="n">
+        <v>298.17</v>
+      </c>
+      <c r="P475" t="n">
+        <v>296.93</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>305.55</v>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>267.23</v>
+      </c>
+      <c r="C476" t="n">
+        <v>287.45</v>
+      </c>
+      <c r="D476" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="E476" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="F476" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="G476" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="H476" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="I476" t="n">
+        <v>330.16</v>
+      </c>
+      <c r="J476" t="n">
+        <v>304.95</v>
+      </c>
+      <c r="K476" t="n">
+        <v>289.17</v>
+      </c>
+      <c r="L476" t="n">
+        <v>280.77</v>
+      </c>
+      <c r="M476" t="n">
+        <v>291.52</v>
+      </c>
+      <c r="N476" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="O476" t="n">
+        <v>293.94</v>
+      </c>
+      <c r="P476" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>305.24</v>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>267.23</v>
+      </c>
+      <c r="C477" t="n">
+        <v>287.45</v>
+      </c>
+      <c r="D477" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="E477" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="F477" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="G477" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="H477" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="I477" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="J477" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="K477" t="n">
+        <v>289.17</v>
+      </c>
+      <c r="L477" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="M477" t="n">
+        <v>291.52</v>
+      </c>
+      <c r="N477" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="O477" t="n">
+        <v>293.94</v>
+      </c>
+      <c r="P477" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>305.73</v>
+      </c>
+      <c r="R477" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28676,7 +28976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34029,6 +34329,56 @@
       </c>
       <c r="B535" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -34197,28 +34547,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5633236406293148</v>
+        <v>-0.5584169987091018</v>
       </c>
       <c r="J2" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02415215892586453</v>
+        <v>0.0242454607640501</v>
       </c>
       <c r="M2" t="n">
-        <v>22.60377916315513</v>
+        <v>22.41431934721051</v>
       </c>
       <c r="N2" t="n">
-        <v>742.8187387012679</v>
+        <v>735.2172484641694</v>
       </c>
       <c r="O2" t="n">
-        <v>27.2547012220143</v>
+        <v>27.11488979258757</v>
       </c>
       <c r="P2" t="n">
-        <v>285.1835527499109</v>
+        <v>285.1314252019598</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34279,28 +34629,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.453021565677021</v>
+        <v>-1.444011821085781</v>
       </c>
       <c r="J3" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K3" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1496327800221228</v>
+        <v>0.1510028879969217</v>
       </c>
       <c r="M3" t="n">
-        <v>20.28861863227469</v>
+        <v>20.12975570340702</v>
       </c>
       <c r="N3" t="n">
-        <v>699.6034266342986</v>
+        <v>691.6263414763123</v>
       </c>
       <c r="O3" t="n">
-        <v>26.45001751671062</v>
+        <v>26.29878973406024</v>
       </c>
       <c r="P3" t="n">
-        <v>328.5049479602397</v>
+        <v>328.4104491527529</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34361,28 +34711,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.164616621396653</v>
+        <v>-1.103382593099357</v>
       </c>
       <c r="J4" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K4" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1833844211181913</v>
+        <v>0.1669316688241306</v>
       </c>
       <c r="M4" t="n">
-        <v>14.57067473020613</v>
+        <v>14.76445777598648</v>
       </c>
       <c r="N4" t="n">
-        <v>351.6005298847131</v>
+        <v>357.8113408973967</v>
       </c>
       <c r="O4" t="n">
-        <v>18.75101410283489</v>
+        <v>18.91590179973973</v>
       </c>
       <c r="P4" t="n">
-        <v>336.8800971662593</v>
+        <v>336.2359790399107</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34439,28 +34789,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9084592382310985</v>
+        <v>-0.8576830938618303</v>
       </c>
       <c r="J5" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K5" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1421622330029833</v>
+        <v>0.1285514766455325</v>
       </c>
       <c r="M5" t="n">
-        <v>12.70537850213112</v>
+        <v>12.89319902438693</v>
       </c>
       <c r="N5" t="n">
-        <v>289.9079653438549</v>
+        <v>293.6826719024062</v>
       </c>
       <c r="O5" t="n">
-        <v>17.02668392094758</v>
+        <v>17.13717222596558</v>
       </c>
       <c r="P5" t="n">
-        <v>334.1557048148842</v>
+        <v>333.6215992224954</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34517,28 +34867,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8022890118532284</v>
+        <v>-0.7508742991622143</v>
       </c>
       <c r="J6" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K6" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1286123875632355</v>
+        <v>0.1139838768239999</v>
       </c>
       <c r="M6" t="n">
-        <v>11.76335477461417</v>
+        <v>11.94213481784526</v>
       </c>
       <c r="N6" t="n">
-        <v>250.3227992260232</v>
+        <v>254.5153658216838</v>
       </c>
       <c r="O6" t="n">
-        <v>15.82159281570674</v>
+        <v>15.95353772119788</v>
       </c>
       <c r="P6" t="n">
-        <v>334.6884769213781</v>
+        <v>334.1420346965504</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34595,28 +34945,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8073820417154766</v>
+        <v>-0.760637719667616</v>
       </c>
       <c r="J7" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K7" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1430302618844453</v>
+        <v>0.1286543413967109</v>
       </c>
       <c r="M7" t="n">
-        <v>11.42072535885667</v>
+        <v>11.54680878273669</v>
       </c>
       <c r="N7" t="n">
-        <v>223.8982086636859</v>
+        <v>227.2832088935983</v>
       </c>
       <c r="O7" t="n">
-        <v>14.96322855080701</v>
+        <v>15.07591486091635</v>
       </c>
       <c r="P7" t="n">
-        <v>332.4656774518398</v>
+        <v>331.9688597174509</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34673,28 +35023,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.27729819606808</v>
+        <v>-1.209027073886798</v>
       </c>
       <c r="J8" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K8" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2281031187314269</v>
+        <v>0.2067332633640359</v>
       </c>
       <c r="M8" t="n">
-        <v>13.82867515198559</v>
+        <v>14.01984768292507</v>
       </c>
       <c r="N8" t="n">
-        <v>320.9761668370886</v>
+        <v>329.9073665468412</v>
       </c>
       <c r="O8" t="n">
-        <v>17.91580773610525</v>
+        <v>18.16335229374911</v>
       </c>
       <c r="P8" t="n">
-        <v>333.9941052058239</v>
+        <v>333.2758680660117</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34751,28 +35101,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.179949988588861</v>
+        <v>-1.117016622824788</v>
       </c>
       <c r="J9" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K9" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2402964522348596</v>
+        <v>0.2177245220247179</v>
       </c>
       <c r="M9" t="n">
-        <v>12.36644489339849</v>
+        <v>12.57357281756216</v>
       </c>
       <c r="N9" t="n">
-        <v>257.3037622143171</v>
+        <v>265.0890212958916</v>
       </c>
       <c r="O9" t="n">
-        <v>16.04069082721555</v>
+        <v>16.28155463387608</v>
       </c>
       <c r="P9" t="n">
-        <v>330.3115479231124</v>
+        <v>329.650613197754</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34829,28 +35179,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.07012577676746</v>
+        <v>-1.04921291495486</v>
       </c>
       <c r="J10" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K10" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1799684229714896</v>
+        <v>0.1765845858160302</v>
       </c>
       <c r="M10" t="n">
-        <v>13.78523085522604</v>
+        <v>13.73749135034623</v>
       </c>
       <c r="N10" t="n">
-        <v>302.6752312467337</v>
+        <v>301.2275662218307</v>
       </c>
       <c r="O10" t="n">
-        <v>17.39756394575786</v>
+        <v>17.35590868326492</v>
       </c>
       <c r="P10" t="n">
-        <v>329.0296410753754</v>
+        <v>328.809139499748</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34907,28 +35257,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.205519592816326</v>
+        <v>-1.205005668147728</v>
       </c>
       <c r="J11" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K11" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2136419791270661</v>
+        <v>0.2174608644142391</v>
       </c>
       <c r="M11" t="n">
-        <v>13.5265987610797</v>
+        <v>13.41717081260261</v>
       </c>
       <c r="N11" t="n">
-        <v>311.9956203134787</v>
+        <v>308.2783453894396</v>
       </c>
       <c r="O11" t="n">
-        <v>17.663397756759</v>
+        <v>17.55785708420705</v>
       </c>
       <c r="P11" t="n">
-        <v>325.2710569885636</v>
+        <v>325.2656767633422</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34985,28 +35335,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8519746607351116</v>
+        <v>-0.8626728560464253</v>
       </c>
       <c r="J12" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K12" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1056221156012566</v>
+        <v>0.1099536119357216</v>
       </c>
       <c r="M12" t="n">
-        <v>14.94708347473052</v>
+        <v>14.86895560248516</v>
       </c>
       <c r="N12" t="n">
-        <v>355.422387905521</v>
+        <v>352.339709666361</v>
       </c>
       <c r="O12" t="n">
-        <v>18.85264936038224</v>
+        <v>18.77071414907704</v>
       </c>
       <c r="P12" t="n">
-        <v>314.1493916586199</v>
+        <v>314.2632266417332</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35063,28 +35413,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7450944045899648</v>
+        <v>-0.7493850565186185</v>
       </c>
       <c r="J13" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K13" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L13" t="n">
-        <v>0.091638432399202</v>
+        <v>0.09455814119772565</v>
       </c>
       <c r="M13" t="n">
-        <v>14.40118760784886</v>
+        <v>14.27902847365677</v>
       </c>
       <c r="N13" t="n">
-        <v>320.8950370054493</v>
+        <v>317.1794097862481</v>
       </c>
       <c r="O13" t="n">
-        <v>17.91354339614163</v>
+        <v>17.80953143084478</v>
       </c>
       <c r="P13" t="n">
-        <v>317.0742065225967</v>
+        <v>317.1194318307858</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35141,28 +35491,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.093676373258798</v>
+        <v>-1.085977837534633</v>
       </c>
       <c r="J14" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K14" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1488239051561017</v>
+        <v>0.149921262558895</v>
       </c>
       <c r="M14" t="n">
-        <v>15.90197158067333</v>
+        <v>15.78025723682988</v>
       </c>
       <c r="N14" t="n">
-        <v>398.6626112527861</v>
+        <v>394.1959633822925</v>
       </c>
       <c r="O14" t="n">
-        <v>19.96653728749144</v>
+        <v>19.85436887393534</v>
       </c>
       <c r="P14" t="n">
-        <v>320.6645015802626</v>
+        <v>320.583485189838</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35219,28 +35569,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.966310932047918</v>
+        <v>-0.9461075066200261</v>
       </c>
       <c r="J15" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K15" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1706953132121561</v>
+        <v>0.1671809380179338</v>
       </c>
       <c r="M15" t="n">
-        <v>12.88256971680523</v>
+        <v>12.86189459962044</v>
       </c>
       <c r="N15" t="n">
-        <v>263.9180862444907</v>
+        <v>262.4234598170344</v>
       </c>
       <c r="O15" t="n">
-        <v>16.24555589213526</v>
+        <v>16.19948949248199</v>
       </c>
       <c r="P15" t="n">
-        <v>314.3560557942264</v>
+        <v>314.1433569175989</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -35301,28 +35651,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5751829531545092</v>
+        <v>-0.5595351490925455</v>
       </c>
       <c r="J16" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K16" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0790007452380449</v>
+        <v>0.07633594021634493</v>
       </c>
       <c r="M16" t="n">
-        <v>11.89663754798201</v>
+        <v>11.86038133277416</v>
       </c>
       <c r="N16" t="n">
-        <v>224.7033946343152</v>
+        <v>223.2469795731039</v>
       </c>
       <c r="O16" t="n">
-        <v>14.99010989400395</v>
+        <v>14.94145172240984</v>
       </c>
       <c r="P16" t="n">
-        <v>305.1216020680668</v>
+        <v>304.9568060148857</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -35383,28 +35733,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1795158422863162</v>
+        <v>-0.1748749568886162</v>
       </c>
       <c r="J17" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K17" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01305193617827416</v>
+        <v>0.0126624412774502</v>
       </c>
       <c r="M17" t="n">
-        <v>7.862585478465309</v>
+        <v>7.799552382159595</v>
       </c>
       <c r="N17" t="n">
-        <v>139.6742302792959</v>
+        <v>138.2773063388865</v>
       </c>
       <c r="O17" t="n">
-        <v>11.81838526530997</v>
+        <v>11.7591371426175</v>
       </c>
       <c r="P17" t="n">
-        <v>308.9887611191006</v>
+        <v>308.9393843125318</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -35446,7 +35796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R472"/>
+  <dimension ref="A1:R477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78558,7 +78908,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>-45.90724610271799,170.55058404778313</t>
+          <t>-45.907132376035875,170.55060106544133</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -78598,7 +78948,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>-45.907021550974925,170.54339920481937</t>
+          <t>-45.90694247203104,170.54339905589083</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -78608,12 +78958,12 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>-45.907030912864286,170.54161270600085</t>
+          <t>-45.9069570037378,170.54161626922425</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>-45.9070589203308,170.54070605531982</t>
+          <t>-45.906977142513725,170.54070619364037</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -78632,6 +78982,466 @@
         </is>
       </c>
       <c r="R472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-45.90685301715533,170.55156912663662</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-45.907051040427106,170.55061323616493</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-45.907261213328205,170.54968061926309</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-45.907217944117036,170.54878468379948</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-45.907218827253146,170.5478862737719</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-45.90720131314605,170.5469892725878</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-45.90721493741289,170.54609108603296</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-45.90718239313679,170.54519538439675</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-45.907044874013124,170.5443054283933</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-45.90688876312319,170.543398954739</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-45.906838579411776,170.54250897513342</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-45.906911687192505,170.54161845396766</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-45.90692586269389,170.54070628037329</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-45.90693597629252,170.5397916545675</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-45.90698239656777,170.53887447527913</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>-45.907111163977916,170.53798222939312</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-45.906774758576816,170.5515844815433</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-45.90693615051907,170.55063042774515</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-45.90723868916303,170.54968291688442</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-45.90719684651363,170.54878664004625</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-45.90719805541608,170.54788719959646</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-45.90718727869484,170.54698933474634</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-45.907187948093124,170.5460912058663</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-45.90714643506384,170.54519741199366</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-45.90698123905379,170.54430939112643</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-45.90683190545141,170.54339884765486</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-45.90676751260602,170.54251022114116</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-45.90684775849394,170.54162153600774</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-45.90685533044978,170.54070639966562</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-45.90689615467463,170.53978934192833</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-45.906941091408534,170.5388691250647</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>-45.907081711548976,170.53797687915312</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-45.90673678801227,170.55159193162893</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-45.906870384097004,170.55064026868348</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-45.907210242308736,170.549685818658</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-45.90717018273382,170.54878911240655</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-45.90718213933309,170.54788790899386</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-45.90716676680457,170.54698942559307</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-45.907157989948054,170.54609133888056</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-45.90714643506384,170.54519741199366</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>-45.906928120040384,170.54431269899186</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>-45.90678656325709,170.54339876225706</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>-45.906726491765816,170.5425109403526</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>-45.90681152323966,170.5416232829261</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>-45.906807559248264,170.54070648045956</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>-45.90686747951395,170.5397876766206</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>-45.9069050725926,170.53886445959031</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>-45.907074839315506,170.5379756307645</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>-45.90670978077915,170.55159723062667</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>-45.90681678669847,170.55064828869396</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>-45.907210242308736,170.549685818658</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-45.90717018273382,170.54878911240655</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-45.90718213933309,170.54788790899386</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>-45.90712439355734,170.54698961326207</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>-45.907157989948054,170.54609133888056</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-45.90714643506384,170.54519741199366</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>-45.90688578661298,170.54431533520346</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>-45.906750037600325,170.54339869346336</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>-45.906696175925404,170.5425114718736</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-45.90678212143261,170.54162470039844</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>-45.9067756218158,170.54070653447332</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>-45.90682945571139,170.53978546839292</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>-45.90686358823458,170.5388590861771</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>-45.90707207257216,170.53797512816658</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>-45.90670978077915,170.55159723062667</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>-45.90681678669847,170.55064828869396</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>-45.90720790912825,170.54968605665817</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-45.90716829741605,170.5487892872198</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-45.90717719365757,170.54788812942795</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>-45.90712439355734,170.54698961326207</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>-45.90714629457606,170.54609139080785</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-45.90712935497909,170.54519837510094</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-45.90685477805122,170.5443172661831</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-45.906750037600325,170.54339869346336</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>-45.906682052521944,170.54251171949574</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-45.90678212143261,170.54162470039844</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-45.906768064789496,170.5407065472539</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-45.90682945571139,170.53978546839292</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>-45.90686358823458,170.5388590861771</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>-45.90707644581164,170.53797592259556</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R477"/>
+  <dimension ref="A1:R478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28915,7 +28915,7 @@
         <v>267.23</v>
       </c>
       <c r="C477" t="n">
-        <v>287.45</v>
+        <v>289.49</v>
       </c>
       <c r="D477" t="n">
         <v>334.7</v>
@@ -28927,7 +28927,7 @@
         <v>337.31</v>
       </c>
       <c r="G477" t="n">
-        <v>330.17</v>
+        <v>330.32</v>
       </c>
       <c r="H477" t="n">
         <v>331.36</v>
@@ -28962,6 +28962,66 @@
       <c r="R477" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>267.23</v>
+      </c>
+      <c r="C478" t="n">
+        <v>289.49</v>
+      </c>
+      <c r="D478" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="E478" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="F478" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="G478" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="H478" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="I478" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="J478" t="n">
+        <v>299.87</v>
+      </c>
+      <c r="K478" t="n">
+        <v>289.17</v>
+      </c>
+      <c r="L478" t="n">
+        <v>278.38</v>
+      </c>
+      <c r="M478" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="N478" t="n">
+        <v>289.06</v>
+      </c>
+      <c r="O478" t="n">
+        <v>291.36</v>
+      </c>
+      <c r="P478" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>304.28</v>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28976,7 +29036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34379,6 +34439,16 @@
       </c>
       <c r="B540" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -34547,28 +34617,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5584169987091018</v>
+        <v>-0.5595574192523304</v>
       </c>
       <c r="J2" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K2" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0242454607640501</v>
+        <v>0.02444497040000859</v>
       </c>
       <c r="M2" t="n">
-        <v>22.41431934721051</v>
+        <v>22.37084204801386</v>
       </c>
       <c r="N2" t="n">
-        <v>735.2172484641694</v>
+        <v>733.6434125581877</v>
       </c>
       <c r="O2" t="n">
-        <v>27.11488979258757</v>
+        <v>27.08585262749149</v>
       </c>
       <c r="P2" t="n">
-        <v>285.1314252019598</v>
+        <v>285.1436118981154</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34629,28 +34699,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.444011821085781</v>
+        <v>-1.443216265815161</v>
       </c>
       <c r="J3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K3" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1510028879969217</v>
+        <v>0.1514271309559527</v>
       </c>
       <c r="M3" t="n">
-        <v>20.12975570340702</v>
+        <v>20.08225654966071</v>
       </c>
       <c r="N3" t="n">
-        <v>691.6263414763123</v>
+        <v>690.157877241031</v>
       </c>
       <c r="O3" t="n">
-        <v>26.29878973406024</v>
+        <v>26.27085604317132</v>
       </c>
       <c r="P3" t="n">
-        <v>328.4104491527529</v>
+        <v>328.402084830058</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34711,28 +34781,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.103382593099357</v>
+        <v>-1.092636237450844</v>
       </c>
       <c r="J4" t="n">
+        <v>477</v>
+      </c>
+      <c r="K4" t="n">
         <v>476</v>
       </c>
-      <c r="K4" t="n">
-        <v>475</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1669316688241306</v>
+        <v>0.1642282924693906</v>
       </c>
       <c r="M4" t="n">
-        <v>14.76445777598648</v>
+        <v>14.79473518197254</v>
       </c>
       <c r="N4" t="n">
-        <v>357.8113408973967</v>
+        <v>358.6183913570874</v>
       </c>
       <c r="O4" t="n">
-        <v>18.91590179973973</v>
+        <v>18.93722237703004</v>
       </c>
       <c r="P4" t="n">
-        <v>336.2359790399107</v>
+        <v>336.1226408839214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34789,28 +34859,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8576830938618303</v>
+        <v>-0.8492244626561606</v>
       </c>
       <c r="J5" t="n">
+        <v>477</v>
+      </c>
+      <c r="K5" t="n">
         <v>476</v>
       </c>
-      <c r="K5" t="n">
-        <v>475</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1285514766455325</v>
+        <v>0.1264657329305693</v>
       </c>
       <c r="M5" t="n">
-        <v>12.89319902438693</v>
+        <v>12.92051153814899</v>
       </c>
       <c r="N5" t="n">
-        <v>293.6826719024062</v>
+        <v>294.0314212471997</v>
       </c>
       <c r="O5" t="n">
-        <v>17.13717222596558</v>
+        <v>17.14734443717743</v>
       </c>
       <c r="P5" t="n">
-        <v>333.6215992224954</v>
+        <v>333.5323889176813</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34867,28 +34937,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7508742991622143</v>
+        <v>-0.7422392481590147</v>
       </c>
       <c r="J6" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K6" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1139838768239999</v>
+        <v>0.1117193375714219</v>
       </c>
       <c r="M6" t="n">
-        <v>11.94213481784526</v>
+        <v>11.96851169193996</v>
       </c>
       <c r="N6" t="n">
-        <v>254.5153658216838</v>
+        <v>254.9648806826235</v>
       </c>
       <c r="O6" t="n">
-        <v>15.95353772119788</v>
+        <v>15.96761975632635</v>
       </c>
       <c r="P6" t="n">
-        <v>334.1420346965504</v>
+        <v>334.0500223579907</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34945,28 +35015,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.760637719667616</v>
+        <v>-0.7537017431441592</v>
       </c>
       <c r="J7" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K7" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1286543413967109</v>
+        <v>0.1267909037391372</v>
       </c>
       <c r="M7" t="n">
-        <v>11.54680878273669</v>
+        <v>11.55882845044795</v>
       </c>
       <c r="N7" t="n">
-        <v>227.2832088935983</v>
+        <v>227.4406099056573</v>
       </c>
       <c r="O7" t="n">
-        <v>15.07591486091635</v>
+        <v>15.08113423803585</v>
       </c>
       <c r="P7" t="n">
-        <v>331.9688597174509</v>
+        <v>331.894945182645</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35023,28 +35093,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.209027073886798</v>
+        <v>-1.197947162345343</v>
       </c>
       <c r="J8" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K8" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2067332633640359</v>
+        <v>0.203625880479661</v>
       </c>
       <c r="M8" t="n">
-        <v>14.01984768292507</v>
+        <v>14.04573566887497</v>
       </c>
       <c r="N8" t="n">
-        <v>329.9073665468412</v>
+        <v>330.869016537708</v>
       </c>
       <c r="O8" t="n">
-        <v>18.16335229374911</v>
+        <v>18.18980529136329</v>
       </c>
       <c r="P8" t="n">
-        <v>333.2758680660117</v>
+        <v>333.1589963666132</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35101,28 +35171,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.117016622824788</v>
+        <v>-1.107252349821484</v>
       </c>
       <c r="J9" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K9" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2177245220247179</v>
+        <v>0.2146604332789138</v>
       </c>
       <c r="M9" t="n">
-        <v>12.57357281756216</v>
+        <v>12.5996573343639</v>
       </c>
       <c r="N9" t="n">
-        <v>265.0890212958916</v>
+        <v>265.8237767537118</v>
       </c>
       <c r="O9" t="n">
-        <v>16.28155463387608</v>
+        <v>16.30410306498679</v>
       </c>
       <c r="P9" t="n">
-        <v>329.650613197754</v>
+        <v>329.5477973790935</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35179,28 +35249,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.04921291495486</v>
+        <v>-1.049480420403071</v>
       </c>
       <c r="J10" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K10" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1765845858160302</v>
+        <v>0.1772942558686423</v>
       </c>
       <c r="M10" t="n">
-        <v>13.73749135034623</v>
+        <v>13.71015747767544</v>
       </c>
       <c r="N10" t="n">
-        <v>301.2275662218307</v>
+        <v>300.5943647052341</v>
       </c>
       <c r="O10" t="n">
-        <v>17.35590868326492</v>
+        <v>17.33765741688404</v>
       </c>
       <c r="P10" t="n">
-        <v>328.809139499748</v>
+        <v>328.8119697597501</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35257,28 +35327,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.205005668147728</v>
+        <v>-1.206436466776617</v>
       </c>
       <c r="J11" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K11" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2174608644142391</v>
+        <v>0.218591840431608</v>
       </c>
       <c r="M11" t="n">
-        <v>13.41717081260261</v>
+        <v>13.39640430073526</v>
       </c>
       <c r="N11" t="n">
-        <v>308.2783453894396</v>
+        <v>307.6543578360869</v>
       </c>
       <c r="O11" t="n">
-        <v>17.55785708420705</v>
+        <v>17.54007861544773</v>
       </c>
       <c r="P11" t="n">
-        <v>325.2656767633422</v>
+        <v>325.2807839295104</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35335,28 +35405,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8626728560464253</v>
+        <v>-0.8676925434073659</v>
       </c>
       <c r="J12" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K12" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1099536119357216</v>
+        <v>0.1114296855442831</v>
       </c>
       <c r="M12" t="n">
-        <v>14.86895560248516</v>
+        <v>14.86475749343342</v>
       </c>
       <c r="N12" t="n">
-        <v>352.339709666361</v>
+        <v>351.9269769714368</v>
       </c>
       <c r="O12" t="n">
-        <v>18.77071414907704</v>
+        <v>18.7597168681043</v>
       </c>
       <c r="P12" t="n">
-        <v>314.2632266417332</v>
+        <v>314.3166937720036</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35413,28 +35483,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7493850565186185</v>
+        <v>-0.7521716505204905</v>
       </c>
       <c r="J13" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K13" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09455814119772565</v>
+        <v>0.09554226907045271</v>
       </c>
       <c r="M13" t="n">
-        <v>14.27902847365677</v>
+        <v>14.26189840899433</v>
       </c>
       <c r="N13" t="n">
-        <v>317.1794097862481</v>
+        <v>316.6141202452505</v>
       </c>
       <c r="O13" t="n">
-        <v>17.80953143084478</v>
+        <v>17.79365393181655</v>
       </c>
       <c r="P13" t="n">
-        <v>317.1194318307858</v>
+        <v>317.1488595603396</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35491,28 +35561,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.085977837534633</v>
+        <v>-1.086870285999921</v>
       </c>
       <c r="J14" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K14" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L14" t="n">
-        <v>0.149921262558895</v>
+        <v>0.1506837595380808</v>
       </c>
       <c r="M14" t="n">
-        <v>15.78025723682988</v>
+        <v>15.75143122360642</v>
       </c>
       <c r="N14" t="n">
-        <v>394.1959633822925</v>
+        <v>393.375107947671</v>
       </c>
       <c r="O14" t="n">
-        <v>19.85436887393534</v>
+        <v>19.83368619162033</v>
       </c>
       <c r="P14" t="n">
-        <v>320.583485189838</v>
+        <v>320.5929063631734</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35569,28 +35639,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9461075066200261</v>
+        <v>-0.9450428673894731</v>
       </c>
       <c r="J15" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K15" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1671809380179338</v>
+        <v>0.1674665760459992</v>
       </c>
       <c r="M15" t="n">
-        <v>12.86189459962044</v>
+        <v>12.84090128435467</v>
       </c>
       <c r="N15" t="n">
-        <v>262.4234598170344</v>
+        <v>261.8862885724868</v>
       </c>
       <c r="O15" t="n">
-        <v>16.19948949248199</v>
+        <v>16.18290111730548</v>
       </c>
       <c r="P15" t="n">
-        <v>314.1433569175989</v>
+        <v>314.1321138277278</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -35651,28 +35721,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5595351490925455</v>
+        <v>-0.558585043476119</v>
       </c>
       <c r="J16" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K16" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07633594021634493</v>
+        <v>0.07639927786068135</v>
       </c>
       <c r="M16" t="n">
-        <v>11.86038133277416</v>
+        <v>11.84085220342455</v>
       </c>
       <c r="N16" t="n">
-        <v>223.2469795731039</v>
+        <v>222.78722365986</v>
       </c>
       <c r="O16" t="n">
-        <v>14.94145172240984</v>
+        <v>14.92605854403164</v>
       </c>
       <c r="P16" t="n">
-        <v>304.9568060148857</v>
+        <v>304.9467661769586</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -35733,28 +35803,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1748749568886162</v>
+        <v>-0.1748533153517266</v>
       </c>
       <c r="J17" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K17" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0126624412774502</v>
+        <v>0.01271430510573246</v>
       </c>
       <c r="M17" t="n">
-        <v>7.799552382159595</v>
+        <v>7.783156424404445</v>
       </c>
       <c r="N17" t="n">
-        <v>138.2773063388865</v>
+        <v>137.9849715012269</v>
       </c>
       <c r="O17" t="n">
-        <v>11.7591371426175</v>
+        <v>11.74670045166841</v>
       </c>
       <c r="P17" t="n">
-        <v>308.9393843125318</v>
+        <v>308.9391532859764</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -35796,7 +35866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R477"/>
+  <dimension ref="A1:R478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79368,7 +79438,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>-45.90681678669847,170.55064828869396</t>
+          <t>-45.90683504023668,170.55064555734012</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -79388,7 +79458,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>-45.90712439355734,170.54698961326207</t>
+          <t>-45.907125743023826,170.54698960728538</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -79444,6 +79514,98 @@
       <c r="R477" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>-45.90670978077915,170.55159723062667</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>-45.90683504023668,170.55064555734012</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>-45.907200191685085,170.54968684388942</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-45.90715330465089,170.5487906774008</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-45.9071619070241,170.5478888107693</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-45.907111708572444,170.5469896694429</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>-45.90712398340481,170.54609148986873</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-45.90709474533346,170.54520032665792</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-45.90684012762922,170.54431817850002</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-45.906750037600325,170.54339869346336</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-45.90667467596727,170.5425118488269</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-45.90676710583078,170.54162542430547</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-45.90675510988725,170.54070656916338</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-45.90680626388843,170.53978412153162</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>-45.90686358823458,170.5388590861771</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>-45.90706350459275,170.53797357173454</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R478"/>
+  <dimension ref="A1:R481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28915,7 +28915,7 @@
         <v>267.23</v>
       </c>
       <c r="C477" t="n">
-        <v>289.49</v>
+        <v>287.45</v>
       </c>
       <c r="D477" t="n">
         <v>334.7</v>
@@ -28954,7 +28954,7 @@
         <v>293.94</v>
       </c>
       <c r="P477" t="n">
-        <v>292.3</v>
+        <v>292.25</v>
       </c>
       <c r="Q477" t="n">
         <v>305.73</v>
@@ -28975,7 +28975,7 @@
         <v>267.23</v>
       </c>
       <c r="C478" t="n">
-        <v>289.49</v>
+        <v>287.45</v>
       </c>
       <c r="D478" t="n">
         <v>333.84</v>
@@ -28999,7 +28999,7 @@
         <v>299.87</v>
       </c>
       <c r="K478" t="n">
-        <v>289.17</v>
+        <v>288.24</v>
       </c>
       <c r="L478" t="n">
         <v>278.38</v>
@@ -29014,7 +29014,7 @@
         <v>291.36</v>
       </c>
       <c r="P478" t="n">
-        <v>292.3</v>
+        <v>292.25</v>
       </c>
       <c r="Q478" t="n">
         <v>304.28</v>
@@ -29022,6 +29022,186 @@
       <c r="R478" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>260.89</v>
+      </c>
+      <c r="C479" t="n">
+        <v>284.51</v>
+      </c>
+      <c r="D479" t="n">
+        <v>332.15</v>
+      </c>
+      <c r="E479" t="n">
+        <v>330.93</v>
+      </c>
+      <c r="F479" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="G479" t="n">
+        <v>328.04</v>
+      </c>
+      <c r="H479" t="n">
+        <v>327.94</v>
+      </c>
+      <c r="I479" t="n">
+        <v>322.73</v>
+      </c>
+      <c r="J479" t="n">
+        <v>298.74</v>
+      </c>
+      <c r="K479" t="n">
+        <v>288.19</v>
+      </c>
+      <c r="L479" t="n">
+        <v>278.68</v>
+      </c>
+      <c r="M479" t="n">
+        <v>289.68</v>
+      </c>
+      <c r="N479" t="n">
+        <v>287.41</v>
+      </c>
+      <c r="O479" t="n">
+        <v>289.98</v>
+      </c>
+      <c r="P479" t="n">
+        <v>290.46</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>303.26</v>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>262.58</v>
+      </c>
+      <c r="C480" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="D480" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="E480" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="F480" t="n">
+        <v>334.89</v>
+      </c>
+      <c r="G480" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="H480" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="I480" t="n">
+        <v>321.47</v>
+      </c>
+      <c r="J480" t="n">
+        <v>298.81</v>
+      </c>
+      <c r="K480" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="L480" t="n">
+        <v>279.04</v>
+      </c>
+      <c r="M480" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="N480" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="O480" t="n">
+        <v>289.23</v>
+      </c>
+      <c r="P480" t="n">
+        <v>288.99</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>303.26</v>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>257.74</v>
+      </c>
+      <c r="C481" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="D481" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="E481" t="n">
+        <v>329.06</v>
+      </c>
+      <c r="F481" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="G481" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="H481" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="I481" t="n">
+        <v>317.61</v>
+      </c>
+      <c r="J481" t="n">
+        <v>295.23</v>
+      </c>
+      <c r="K481" t="n">
+        <v>284.31</v>
+      </c>
+      <c r="L481" t="n">
+        <v>275.97</v>
+      </c>
+      <c r="M481" t="n">
+        <v>286.26</v>
+      </c>
+      <c r="N481" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="O481" t="n">
+        <v>285.64</v>
+      </c>
+      <c r="P481" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>302.27</v>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29036,7 +29216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34449,6 +34629,36 @@
       </c>
       <c r="B541" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -34617,28 +34827,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5595574192523304</v>
+        <v>-0.5709525181878996</v>
       </c>
       <c r="J2" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02444497040000859</v>
+        <v>0.02572918375462296</v>
       </c>
       <c r="M2" t="n">
-        <v>22.37084204801386</v>
+        <v>22.27681299778502</v>
       </c>
       <c r="N2" t="n">
-        <v>733.6434125581877</v>
+        <v>729.5202543921102</v>
       </c>
       <c r="O2" t="n">
-        <v>27.08585262749149</v>
+        <v>27.00963262230922</v>
       </c>
       <c r="P2" t="n">
-        <v>285.1436118981154</v>
+        <v>285.2659545856248</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34699,28 +34909,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.443216265815161</v>
+        <v>-1.452361574232358</v>
       </c>
       <c r="J3" t="n">
+        <v>480</v>
+      </c>
+      <c r="K3" t="n">
         <v>477</v>
       </c>
-      <c r="K3" t="n">
-        <v>474</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1514271309559527</v>
+        <v>0.1547173366349619</v>
       </c>
       <c r="M3" t="n">
-        <v>20.08225654966071</v>
+        <v>20.01295037649618</v>
       </c>
       <c r="N3" t="n">
-        <v>690.157877241031</v>
+        <v>686.1176394881669</v>
       </c>
       <c r="O3" t="n">
-        <v>26.27085604317132</v>
+        <v>26.19384735941184</v>
       </c>
       <c r="P3" t="n">
-        <v>328.402084830058</v>
+        <v>328.4987065198154</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34781,28 +34991,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.092636237450844</v>
+        <v>-1.064798838923051</v>
       </c>
       <c r="J4" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K4" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1642282924693906</v>
+        <v>0.1577033364289648</v>
       </c>
       <c r="M4" t="n">
-        <v>14.79473518197254</v>
+        <v>14.86110513857203</v>
       </c>
       <c r="N4" t="n">
-        <v>358.6183913570874</v>
+        <v>359.8814323283706</v>
       </c>
       <c r="O4" t="n">
-        <v>18.93722237703004</v>
+        <v>18.97054117120465</v>
       </c>
       <c r="P4" t="n">
-        <v>336.1226408839214</v>
+        <v>335.8277817799896</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34859,28 +35069,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8492244626561606</v>
+        <v>-0.8263264526647797</v>
       </c>
       <c r="J5" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K5" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1264657329305693</v>
+        <v>0.1210822227499001</v>
       </c>
       <c r="M5" t="n">
-        <v>12.92051153814899</v>
+        <v>12.98643841560136</v>
       </c>
       <c r="N5" t="n">
-        <v>294.0314212471997</v>
+        <v>294.5583097142919</v>
       </c>
       <c r="O5" t="n">
-        <v>17.14734443717743</v>
+        <v>17.16270111941276</v>
       </c>
       <c r="P5" t="n">
-        <v>333.5323889176813</v>
+        <v>333.2898419108661</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34937,28 +35147,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7422392481590147</v>
+        <v>-0.7180752372533501</v>
       </c>
       <c r="J6" t="n">
+        <v>480</v>
+      </c>
+      <c r="K6" t="n">
         <v>477</v>
       </c>
-      <c r="K6" t="n">
-        <v>474</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1117193375714219</v>
+        <v>0.1056007359440241</v>
       </c>
       <c r="M6" t="n">
-        <v>11.96851169193996</v>
+        <v>12.03632175987978</v>
       </c>
       <c r="N6" t="n">
-        <v>254.9648806826235</v>
+        <v>255.9508718750118</v>
       </c>
       <c r="O6" t="n">
-        <v>15.96761975632635</v>
+        <v>15.99846467243066</v>
       </c>
       <c r="P6" t="n">
-        <v>334.0500223579907</v>
+        <v>333.7914381904178</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35015,28 +35225,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7537017431441592</v>
+        <v>-0.7354712876677053</v>
       </c>
       <c r="J7" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K7" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1267909037391372</v>
+        <v>0.1221824890136478</v>
       </c>
       <c r="M7" t="n">
-        <v>11.55882845044795</v>
+        <v>11.58091904762382</v>
       </c>
       <c r="N7" t="n">
-        <v>227.4406099056573</v>
+        <v>227.4880368916095</v>
       </c>
       <c r="O7" t="n">
-        <v>15.08113423803585</v>
+        <v>15.08270655060323</v>
       </c>
       <c r="P7" t="n">
-        <v>331.894945182645</v>
+        <v>331.6998446792002</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35093,28 +35303,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.197947162345343</v>
+        <v>-1.168026433632469</v>
       </c>
       <c r="J8" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K8" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L8" t="n">
-        <v>0.203625880479661</v>
+        <v>0.1956837670570124</v>
       </c>
       <c r="M8" t="n">
-        <v>14.04573566887497</v>
+        <v>14.10620777067657</v>
       </c>
       <c r="N8" t="n">
-        <v>330.869016537708</v>
+        <v>332.8463434317564</v>
       </c>
       <c r="O8" t="n">
-        <v>18.18980529136329</v>
+        <v>18.24407694107204</v>
       </c>
       <c r="P8" t="n">
-        <v>333.1589963666132</v>
+        <v>332.8420324372457</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35171,28 +35381,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.107252349821484</v>
+        <v>-1.082776724948247</v>
       </c>
       <c r="J9" t="n">
+        <v>480</v>
+      </c>
+      <c r="K9" t="n">
         <v>477</v>
       </c>
-      <c r="K9" t="n">
-        <v>474</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2146604332789138</v>
+        <v>0.2076691926618527</v>
       </c>
       <c r="M9" t="n">
-        <v>12.5996573343639</v>
+        <v>12.65346040082934</v>
       </c>
       <c r="N9" t="n">
-        <v>265.8237767537118</v>
+        <v>266.8983173259435</v>
       </c>
       <c r="O9" t="n">
-        <v>16.30410306498679</v>
+        <v>16.33702290277955</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5477973790935</v>
+        <v>329.2889662960557</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35249,28 +35459,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.049480420403071</v>
+        <v>-1.052819901168207</v>
       </c>
       <c r="J10" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K10" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1772942558686423</v>
+        <v>0.1801171481759533</v>
       </c>
       <c r="M10" t="n">
-        <v>13.71015747767544</v>
+        <v>13.64372341830349</v>
       </c>
       <c r="N10" t="n">
-        <v>300.5943647052341</v>
+        <v>298.7746542759555</v>
       </c>
       <c r="O10" t="n">
-        <v>17.33765741688404</v>
+        <v>17.28509919774704</v>
       </c>
       <c r="P10" t="n">
-        <v>328.8119697597501</v>
+        <v>328.8474817011464</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35327,28 +35537,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.206436466776617</v>
+        <v>-1.213573896045732</v>
       </c>
       <c r="J11" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K11" t="n">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L11" t="n">
-        <v>0.218591840431608</v>
+        <v>0.2227290615564367</v>
       </c>
       <c r="M11" t="n">
-        <v>13.39640430073526</v>
+        <v>13.34925987195691</v>
       </c>
       <c r="N11" t="n">
-        <v>307.6543578360869</v>
+        <v>305.9585844650787</v>
       </c>
       <c r="O11" t="n">
-        <v>17.54007861544773</v>
+        <v>17.49167186020475</v>
       </c>
       <c r="P11" t="n">
-        <v>325.2807839295104</v>
+        <v>325.3564888079036</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35405,28 +35615,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8676925434073659</v>
+        <v>-0.8829722490904817</v>
       </c>
       <c r="J12" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K12" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1114296855442831</v>
+        <v>0.1159593232598147</v>
       </c>
       <c r="M12" t="n">
-        <v>14.86475749343342</v>
+        <v>14.85272758349607</v>
       </c>
       <c r="N12" t="n">
-        <v>351.9269769714368</v>
+        <v>350.7487122677732</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7597168681043</v>
+        <v>18.7282864210203</v>
       </c>
       <c r="P12" t="n">
-        <v>314.3166937720036</v>
+        <v>314.4801858557803</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35483,28 +35693,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7521716505204905</v>
+        <v>-0.7619313202961228</v>
       </c>
       <c r="J13" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K13" t="n">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09554226907045271</v>
+        <v>0.0988255607166042</v>
       </c>
       <c r="M13" t="n">
-        <v>14.26189840899433</v>
+        <v>14.21692784925005</v>
       </c>
       <c r="N13" t="n">
-        <v>316.6141202452505</v>
+        <v>315.0645607906293</v>
       </c>
       <c r="O13" t="n">
-        <v>17.79365393181655</v>
+        <v>17.75005805034534</v>
       </c>
       <c r="P13" t="n">
-        <v>317.1488595603396</v>
+        <v>317.2524065904862</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35561,28 +35771,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.086870285999921</v>
+        <v>-1.092786828015486</v>
       </c>
       <c r="J14" t="n">
+        <v>480</v>
+      </c>
+      <c r="K14" t="n">
         <v>477</v>
       </c>
-      <c r="K14" t="n">
-        <v>474</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1506837595380808</v>
+        <v>0.1537133031666242</v>
       </c>
       <c r="M14" t="n">
-        <v>15.75143122360642</v>
+        <v>15.6817882086882</v>
       </c>
       <c r="N14" t="n">
-        <v>393.375107947671</v>
+        <v>391.0761839410758</v>
       </c>
       <c r="O14" t="n">
-        <v>19.83368619162033</v>
+        <v>19.77564623321008</v>
       </c>
       <c r="P14" t="n">
-        <v>320.5929063631734</v>
+        <v>320.6556657062694</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35639,28 +35849,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9450428673894731</v>
+        <v>-0.9453972128052848</v>
       </c>
       <c r="J15" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K15" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1674665760459992</v>
+        <v>0.1693922552671849</v>
       </c>
       <c r="M15" t="n">
-        <v>12.84090128435467</v>
+        <v>12.77048320129702</v>
       </c>
       <c r="N15" t="n">
-        <v>261.8862885724868</v>
+        <v>260.2651299789301</v>
       </c>
       <c r="O15" t="n">
-        <v>16.18290111730548</v>
+        <v>16.13273473342106</v>
       </c>
       <c r="P15" t="n">
-        <v>314.1321138277278</v>
+        <v>314.1359014010785</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -35721,28 +35931,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.558585043476119</v>
+        <v>-0.5602922428513435</v>
       </c>
       <c r="J16" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K16" t="n">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07639927786068135</v>
+        <v>0.07775110932003704</v>
       </c>
       <c r="M16" t="n">
-        <v>11.84085220342455</v>
+        <v>11.77670882416985</v>
       </c>
       <c r="N16" t="n">
-        <v>222.78722365986</v>
+        <v>221.4183062534364</v>
       </c>
       <c r="O16" t="n">
-        <v>14.92605854403164</v>
+        <v>14.88013125793709</v>
       </c>
       <c r="P16" t="n">
-        <v>304.9467661769586</v>
+        <v>304.9649148403012</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -35803,28 +36013,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1748533153517266</v>
+        <v>-0.1763688975709514</v>
       </c>
       <c r="J17" t="n">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K17" t="n">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01271430510573246</v>
+        <v>0.01310089724113772</v>
       </c>
       <c r="M17" t="n">
-        <v>7.783156424404445</v>
+        <v>7.743479026482205</v>
       </c>
       <c r="N17" t="n">
-        <v>137.9849715012269</v>
+        <v>137.1267996312471</v>
       </c>
       <c r="O17" t="n">
-        <v>11.74670045166841</v>
+        <v>11.71011526976772</v>
       </c>
       <c r="P17" t="n">
-        <v>308.9391532859764</v>
+        <v>308.9554097146535</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -35866,7 +36076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R478"/>
+  <dimension ref="A1:R481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79438,7 +79648,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>-45.90683504023668,170.55064555734012</t>
+          <t>-45.90681678669847,170.55064828869396</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -79503,7 +79713,7 @@
       </c>
       <c r="P477" t="inlineStr">
         <is>
-          <t>-45.90686358823458,170.5388590861771</t>
+          <t>-45.90686314023936,170.53885902814892</t>
         </is>
       </c>
       <c r="Q477" t="inlineStr">
@@ -79530,7 +79740,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>-45.90683504023668,170.55064555734012</t>
+          <t>-45.90681678669847,170.55064828869396</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -79570,7 +79780,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>-45.906750037600325,170.54339869346336</t>
+          <t>-45.906741670885815,170.54339867770508</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -79595,7 +79805,7 @@
       </c>
       <c r="P478" t="inlineStr">
         <is>
-          <t>-45.90686358823458,170.5388590861771</t>
+          <t>-45.90686314023936,170.53885902814892</t>
         </is>
       </c>
       <c r="Q478" t="inlineStr">
@@ -79606,6 +79816,282 @@
       <c r="R478" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>-45.90665327059355,170.5516083182801</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>-45.90679048012843,170.55065222505326</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>-45.907185026011845,170.5496883908896</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-45.90714342917677,170.5487915930884</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-45.90716181710272,170.5478888147772</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>-45.90710523113333,170.54698969813094</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-45.90711552675117,170.5460915274159</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-45.907079642942556,170.5452011782454</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-45.90682997120167,170.54431881096474</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-45.90674122106245,170.54339867685786</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-45.90667737470678,170.5425118015106</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-45.906765577296454,170.5416254979966</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-45.90674026572839,170.54070659426785</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-45.906793858959844,170.53978340111772</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>-45.90684710201014,170.53885695074044</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>-45.90705440111461,170.53797191802593</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>-45.906668334034386,170.55160536274084</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>-45.906789495869006,170.5506523723319</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>-45.907172193519024,170.54968969988894</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-45.90714028698046,170.54879188444346</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-45.90715543268521,170.54788909933725</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-45.90710073291173,170.54698971805317</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-45.90710877942114,170.5460915573737</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-45.90706831614934,170.54520181693562</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-45.9068306003609,170.54431877178553</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-45.9067404113804,170.54339867533287</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-45.906680613194204,170.5425117447311</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-45.90676350927943,170.54162559769628</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>-45.90673891625941,170.54070659655008</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-45.90678711715082,170.53978300958852</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>-45.906833930950356,170.53885524471303</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>-45.90705440111461,170.53797191802593</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>-45.906625193765535,170.55161382712078</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>-45.90674923071012,170.55065839736326</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>-45.907151733320575,170.54969178696334</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-45.907126640870715,170.5487931497564</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-45.907136908882215,170.54788992496165</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-45.90708040095002,170.54698980810142</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-45.90708098042129,170.5460916807994</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-45.907033616608054,170.5452037735557</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-45.90679842336015,170.54432077552136</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-45.90670631476953,170.5433986111131</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-45.90665299609309,170.54251222893396</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-45.90673482678236,170.54162698048702</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>-45.906707608578756,170.54070664949703</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-45.9067548463582,170.5397811354696</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>-45.90680534885448,170.5388515425198</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>-45.90704556538579,170.5379703129563</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
